--- a/data/plc_type eos1550.xlsx
+++ b/data/plc_type eos1550.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\2025\2025 leybold 图论\lbgraph\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F02BB4-A8A3-481F-8177-D89E9E4B51EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467597E1-21DF-4049-8D8F-EA15D644C00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3910" yWindow="3660" windowWidth="22710" windowHeight="9320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="22710" windowHeight="9320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="266">
   <si>
     <t>A1,1,DO1.1,RFN_RF on HFN_HN Ein</t>
   </si>
@@ -743,15 +743,6 @@
   </si>
   <si>
     <t>A13-X1</t>
-  </si>
-  <si>
-    <t>GV205</t>
-  </si>
-  <si>
-    <t>GV206</t>
-  </si>
-  <si>
-    <t>GV207</t>
   </si>
   <si>
     <t>交换机</t>
@@ -1628,13 +1619,13 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L1" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="N1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -1668,7 +1659,7 @@
         <v>A1</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M2" t="s">
         <v>199</v>
@@ -1708,7 +1699,7 @@
         <v>A2</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="M3" t="s">
         <v>200</v>
@@ -1748,7 +1739,7 @@
         <v>A3</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M4" t="s">
         <v>201</v>
@@ -1788,7 +1779,7 @@
         <v>A4</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="M5" t="s">
         <v>202</v>
@@ -1828,7 +1819,7 @@
         <v>A5</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M6" t="s">
         <v>203</v>
@@ -1868,7 +1859,7 @@
         <v>A1</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M7" t="s">
         <v>199</v>
@@ -1908,7 +1899,7 @@
         <v>A2</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="M8" t="s">
         <v>200</v>
@@ -1948,7 +1939,7 @@
         <v>A3</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M9" t="s">
         <v>201</v>
@@ -1988,7 +1979,7 @@
         <v>A4</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="M10" t="s">
         <v>202</v>
@@ -2028,7 +2019,7 @@
         <v>T1</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M11" t="s">
         <v>204</v>
@@ -2069,7 +2060,7 @@
         <v xml:space="preserve"> A5</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="M12" t="s">
         <v>205</v>
@@ -2109,13 +2100,13 @@
         <v>A6</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M13" t="s">
         <v>206</v>
       </c>
       <c r="N13" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2149,7 +2140,7 @@
         <v>A7</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="M14" t="s">
         <v>207</v>
@@ -2189,7 +2180,7 @@
         <v>A8</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M15" t="s">
         <v>208</v>
@@ -2229,13 +2220,13 @@
         <v>A9</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="M16" t="s">
         <v>209</v>
       </c>
       <c r="N16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2269,7 +2260,7 @@
         <v>A10</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M17" t="s">
         <v>210</v>
@@ -2309,7 +2300,7 @@
         <v>A11</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="M18" t="s">
         <v>211</v>
@@ -2349,7 +2340,7 @@
         <v>A12</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M19" t="s">
         <v>212</v>
@@ -2389,7 +2380,7 @@
         <v>A13</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="M20" t="s">
         <v>213</v>
@@ -2429,7 +2420,7 @@
         <v>A1</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M21" t="s">
         <v>199</v>
@@ -2469,7 +2460,7 @@
         <v>A2</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M22" t="s">
         <v>200</v>
@@ -2509,7 +2500,7 @@
         <v>A3</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M23" t="s">
         <v>201</v>
@@ -2549,7 +2540,7 @@
         <v>A4</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s">
         <v>202</v>
@@ -2589,7 +2580,7 @@
         <v>A5</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s">
         <v>203</v>
@@ -2629,7 +2620,7 @@
         <v>A6</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s">
         <v>206</v>
@@ -2669,7 +2660,7 @@
         <v>T2</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s">
         <v>214</v>
@@ -2709,7 +2700,7 @@
         <v>A7</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s">
         <v>207</v>
@@ -2749,7 +2740,7 @@
         <v>A8</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M29" t="s">
         <v>208</v>
@@ -2789,7 +2780,7 @@
         <v>A9</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M30" t="s">
         <v>209</v>
@@ -2829,7 +2820,7 @@
         <v>A10</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M31" t="s">
         <v>210</v>
@@ -2869,7 +2860,7 @@
         <v>A11</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M32" t="s">
         <v>211</v>
@@ -2909,7 +2900,7 @@
         <v>A12</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M33" t="s">
         <v>212</v>
@@ -2949,7 +2940,7 @@
         <v>A1</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="M34" t="s">
         <v>199</v>
@@ -2989,7 +2980,7 @@
         <v>A1</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M35" t="s">
         <v>199</v>
@@ -3029,7 +3020,7 @@
         <v>A1.1</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M36" t="s">
         <v>215</v>
@@ -3069,7 +3060,7 @@
         <v>A2</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M37" t="s">
         <v>200</v>
@@ -3109,7 +3100,7 @@
         <v>A2.1</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M38" t="s">
         <v>216</v>
@@ -3149,7 +3140,7 @@
         <v>A3</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M39" t="s">
         <v>201</v>
@@ -3189,7 +3180,7 @@
         <v>A4</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M40" t="s">
         <v>202</v>
@@ -3229,7 +3220,7 @@
         <v>A5</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M41" t="s">
         <v>203</v>
@@ -3269,7 +3260,7 @@
         <v>A5.1</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M42" t="s">
         <v>217</v>
@@ -3309,7 +3300,7 @@
         <v>A6</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M43" t="s">
         <v>206</v>
@@ -3349,7 +3340,7 @@
         <v>A7</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M44" t="s">
         <v>207</v>
@@ -3389,7 +3380,7 @@
         <v>A8</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M45" t="s">
         <v>208</v>
@@ -3429,7 +3420,7 @@
         <v>A13</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M46" t="s">
         <v>213</v>
@@ -3469,7 +3460,7 @@
         <v>A14</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M47" t="s">
         <v>218</v>
@@ -3480,7 +3471,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L48" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="M48" t="s">
         <v>199</v>
@@ -3491,193 +3482,193 @@
     </row>
     <row r="49" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L49" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M49" t="s">
         <v>200</v>
       </c>
       <c r="N49" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L50" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M50" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N50" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="51" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L51" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M51" t="s">
         <v>219</v>
       </c>
       <c r="N51" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="52" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L52" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M52" t="s">
         <v>220</v>
       </c>
       <c r="N52" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L53" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M53" t="s">
         <v>221</v>
       </c>
       <c r="N53" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="54" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L54" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M54" t="s">
         <v>222</v>
       </c>
       <c r="N54" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="55" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L55" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M55" t="s">
         <v>223</v>
       </c>
       <c r="N55" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="56" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L56" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M56" t="s">
         <v>224</v>
       </c>
       <c r="N56" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L57" s="5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="M57" t="s">
         <v>225</v>
       </c>
       <c r="N57" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
     </row>
     <row r="58" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L58" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M58" t="s">
         <v>226</v>
       </c>
       <c r="N58" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L59" s="5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="M59" t="s">
         <v>227</v>
       </c>
       <c r="N59" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L60" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="M60" t="s">
         <v>228</v>
       </c>
       <c r="N60" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O60" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="61" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L61" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M61" t="s">
         <v>229</v>
       </c>
       <c r="N61" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O61" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="62" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L62" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="M62" t="s">
         <v>230</v>
       </c>
       <c r="N62" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O62" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L63" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M63" t="s">
         <v>231</v>
       </c>
       <c r="N63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="O63" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="64" spans="12:15" x14ac:dyDescent="0.3">
       <c r="L64" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M64" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N64" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="O64" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
